--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457417.9329579084</v>
+        <v>457418</v>
       </c>
       <c r="R2" t="n">
-        <v>6243742.956988505</v>
+        <v>6243743</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1998-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457417.9329579084</v>
+        <v>457418</v>
       </c>
       <c r="R3" t="n">
-        <v>6243742.956988505</v>
+        <v>6243743</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1997-08-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1997-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97526</v>
+        <v>97528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97528</v>
+        <v>97529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97529</v>
+        <v>97556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97556</v>
+        <v>97562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97562</v>
+        <v>97569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97569</v>
+        <v>97573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97573</v>
+        <v>97580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63011216</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63013707</v>
       </c>
       <c r="B3" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 5468-2024 artfynd.xlsx
+++ b/artfynd/A 5468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -791,8 +796,16 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58939728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>